--- a/Datas/LuckyGift.xlsx
+++ b/Datas/LuckyGift.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -40,7 +40,13 @@
     <t>LuckyGiftType</t>
   </si>
   <si>
-    <t>PriceCoin</t>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>ThreeKPCoin</t>
+  </si>
+  <si>
+    <t>BuffTypeWeights</t>
   </si>
   <si>
     <t>BuffStrengthWeights</t>
@@ -58,12 +64,15 @@
     <t>HuntingConfig.Enum.ELuckyGiftType</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(map#sep=:|),HuntingConfig.Enum.ELuckyBuffType,int</t>
+  </si>
+  <si>
     <t>(map#sep=:|),HuntingConfig.Enum.ELuckyBuffStrengthType,int</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -79,7 +88,13 @@
     <t>礼包类型</t>
   </si>
   <si>
-    <t>价值金币</t>
+    <t>礼包名称</t>
+  </si>
+  <si>
+    <t>价值3币</t>
+  </si>
+  <si>
+    <t>Buff类型权重(5种效果类型)</t>
   </si>
   <si>
     <t xml:space="preserve">Buff强度权重(弱/中/强) </t>
@@ -91,6 +106,12 @@
     <t>Basic</t>
   </si>
   <si>
+    <t>初级礼包</t>
+  </si>
+  <si>
+    <t>MoreMeat:15|StartSpecialBullet:40|StartEnergy:30|DamageBoost:10|HighTierSpawn:5</t>
+  </si>
+  <si>
     <t>Weak:100|Normal:0|Strong:0</t>
   </si>
   <si>
@@ -100,10 +121,22 @@
     <t>Standard</t>
   </si>
   <si>
+    <t>中级礼包</t>
+  </si>
+  <si>
+    <t>MoreMeat:30|StartSpecialBullet:20|StartEnergy:20|DamageBoost:20|HighTierSpawn:10</t>
+  </si>
+  <si>
     <t>Weak:0|Normal:100|Strong:0</t>
   </si>
   <si>
     <t>Advanced</t>
+  </si>
+  <si>
+    <t>高级礼包</t>
+  </si>
+  <si>
+    <t>MoreMeat:30|StartSpecialBullet:10|StartEnergy:10|DamageBoost:30|HighTierSpawn:20</t>
   </si>
   <si>
     <t>Weak:0|Normal:0|Strong:100</t>
@@ -1067,15 +1100,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="4" width="28.625" customWidth="1"/>
-    <col min="5" max="5" width="56.625" customWidth="1"/>
-    <col min="6" max="6" width="28.625" customWidth="1"/>
+    <col min="1" max="2" width="28.625" customWidth="1"/>
+    <col min="3" max="3" width="48.625" customWidth="1"/>
+    <col min="4" max="5" width="28.625" customWidth="1"/>
+    <col min="6" max="6" width="96.625" customWidth="1"/>
+    <col min="7" max="7" width="78.625" customWidth="1"/>
+    <col min="8" max="8" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6">
+    <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1094,136 +1130,182 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6">
+    <row r="2" ht="28" customHeight="1" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6">
+    <row r="3" ht="28" customHeight="1" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6">
+    <row r="4" ht="28" customHeight="1" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6">
+    <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6">
+    <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3">
         <v>20</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6">
+    <row r="7" ht="28" customHeight="1" spans="1:8">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="3">
         <v>50</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>35</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:6">
+    <row r="8" customHeight="1" spans="1:8">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
-    <row r="9" customHeight="1" spans="1:6">
+    <row r="9" customHeight="1" spans="1:8">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/LuckyGift.xlsx
+++ b/Datas/LuckyGift.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="16785" windowHeight="9165"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>ThreeKPCoin</t>
   </si>
   <si>
+    <t>CostType</t>
+  </si>
+  <si>
     <t>BuffTypeWeights</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>HuntingConfig.Enum.ELuckyGiftCostType</t>
+  </si>
+  <si>
     <t>(map#sep=:|),HuntingConfig.Enum.ELuckyBuffType,int</t>
   </si>
   <si>
@@ -94,6 +100,9 @@
     <t>价值3币</t>
   </si>
   <si>
+    <t>付费方式</t>
+  </si>
+  <si>
     <t>Buff类型权重(5种效果类型)</t>
   </si>
   <si>
@@ -140,6 +149,21 @@
   </si>
   <si>
     <t>Weak:0|Normal:0|Strong:100</t>
+  </si>
+  <si>
+    <t>Special</t>
+  </si>
+  <si>
+    <t>特殊礼包</t>
+  </si>
+  <si>
+    <t>Ad</t>
+  </si>
+  <si>
+    <t>MoreMeat:20|StartSpecialBullet:20|StartEnergy:20|DamageBoost:20|HighTierSpawn:20</t>
+  </si>
+  <si>
+    <t>Weak:33|Normal:33|Strong:34</t>
   </si>
 </sst>
 </file>
@@ -1100,18 +1124,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="3" width="48.625" customWidth="1"/>
     <col min="4" max="5" width="28.625" customWidth="1"/>
-    <col min="6" max="6" width="96.625" customWidth="1"/>
-    <col min="7" max="7" width="78.625" customWidth="1"/>
-    <col min="8" max="8" width="28.625" customWidth="1"/>
+    <col min="6" max="6" width="48.625" customWidth="1"/>
+    <col min="7" max="7" width="96.625" customWidth="1"/>
+    <col min="8" max="8" width="78.625" customWidth="1"/>
+    <col min="9" max="9" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:8">
+    <row r="1" ht="28" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1136,168 +1161,206 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:8">
+    <row r="2" ht="28" customHeight="1" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:8">
+    <row r="3" ht="28" customHeight="1" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:8">
+    <row r="4" ht="28" customHeight="1" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:8">
+    <row r="5" ht="28" customHeight="1" spans="1:9">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3">
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:8">
+    <row r="6" ht="28" customHeight="1" spans="1:9">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3">
         <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:8">
+    <row r="7" ht="28" customHeight="1" spans="1:9">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3">
         <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:8">
+    <row r="8" ht="28" customHeight="1" spans="1:9">
       <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="9" customHeight="1" spans="1:8">
+    <row r="9" customHeight="1" spans="1:9">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
@@ -1306,6 +1369,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/LuckyGift.xlsx
+++ b/Datas/LuckyGift.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16785" windowHeight="9165"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Datas/LuckyGift.xlsx
+++ b/Datas/LuckyGift.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -46,18 +46,12 @@
     <t>ThreeKPCoin</t>
   </si>
   <si>
-    <t>CostType</t>
-  </si>
-  <si>
     <t>BuffTypeWeights</t>
   </si>
   <si>
     <t>BuffStrengthWeights</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -70,9 +64,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>HuntingConfig.Enum.ELuckyGiftCostType</t>
-  </si>
-  <si>
     <t>(map#sep=:|),HuntingConfig.Enum.ELuckyBuffType,int</t>
   </si>
   <si>
@@ -100,40 +91,31 @@
     <t>价值3币</t>
   </si>
   <si>
-    <t>付费方式</t>
-  </si>
-  <si>
     <t>Buff类型权重(5种效果类型)</t>
   </si>
   <si>
     <t xml:space="preserve">Buff强度权重(弱/中/强) </t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>Basic</t>
   </si>
   <si>
     <t>初级礼包</t>
   </si>
   <si>
-    <t>MoreMeat:15|StartSpecialBullet:40|StartEnergy:30|DamageBoost:10|HighTierSpawn:5</t>
+    <t>MoreMeat:15|StartEnergy:30|DamageBoost:10|HighTierSpawn:5</t>
   </si>
   <si>
     <t>Weak:100|Normal:0|Strong:0</t>
   </si>
   <si>
-    <t>示例</t>
-  </si>
-  <si>
     <t>Standard</t>
   </si>
   <si>
     <t>中级礼包</t>
   </si>
   <si>
-    <t>MoreMeat:30|StartSpecialBullet:20|StartEnergy:20|DamageBoost:20|HighTierSpawn:10</t>
+    <t>MoreMeat:30|StartEnergy:20|DamageBoost:20|HighTierSpawn:10</t>
   </si>
   <si>
     <t>Weak:0|Normal:100|Strong:0</t>
@@ -145,25 +127,10 @@
     <t>高级礼包</t>
   </si>
   <si>
-    <t>MoreMeat:30|StartSpecialBullet:10|StartEnergy:10|DamageBoost:30|HighTierSpawn:20</t>
+    <t>MoreMeat:30|StartEnergy:10|DamageBoost:30|HighTierSpawn:20</t>
   </si>
   <si>
     <t>Weak:0|Normal:0|Strong:100</t>
-  </si>
-  <si>
-    <t>Special</t>
-  </si>
-  <si>
-    <t>特殊礼包</t>
-  </si>
-  <si>
-    <t>Ad</t>
-  </si>
-  <si>
-    <t>MoreMeat:20|StartSpecialBullet:20|StartEnergy:20|DamageBoost:20|HighTierSpawn:20</t>
-  </si>
-  <si>
-    <t>Weak:33|Normal:33|Strong:34</t>
   </si>
 </sst>
 </file>
@@ -1124,19 +1091,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="3" width="48.625" customWidth="1"/>
     <col min="4" max="5" width="28.625" customWidth="1"/>
-    <col min="6" max="6" width="48.625" customWidth="1"/>
-    <col min="7" max="7" width="96.625" customWidth="1"/>
-    <col min="8" max="8" width="78.625" customWidth="1"/>
-    <col min="9" max="9" width="28.625" customWidth="1"/>
+    <col min="6" max="6" width="96.625" customWidth="1"/>
+    <col min="7" max="7" width="78.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1158,218 +1123,147 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:9">
+    <row r="5" ht="28" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:9">
+    <row r="6" ht="28" customHeight="1" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
         <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9">
+    <row r="7" ht="28" customHeight="1" spans="1:7">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3">
         <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:9">
+    <row r="8" customHeight="1" spans="1:7">
       <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:9">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
